--- a/www/flightdata/xlsx/eoss-332.xlsx
+++ b/www/flightdata/xlsx/eoss-332.xlsx
@@ -3645,7 +3645,7 @@
         <v>29048.35</v>
       </c>
       <c r="I2">
-        <v>637</v>
+        <v>471</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
